--- a/review_data/ruler/real_questions_template.xlsx
+++ b/review_data/ruler/real_questions_template.xlsx
@@ -1321,7 +1321,7 @@
       <formula1>"English,Hinglish,other"</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"civil, tax or divorce,High Court only or 2026,statute table answers it"</formula1>
+      <formula1>"civil/tax/divorce,High Court only or 2026,statute table answers it"</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes"</formula1>
